--- a/data/trans_bre/IP19C02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 11,01</t>
+          <t>-3,19; 11,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,46; -0,86</t>
+          <t>-20,6; 0,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 16,29</t>
+          <t>-9,49; 15,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 11,62</t>
+          <t>-10,65; 12,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,64; 749,72</t>
+          <t>-76,97; 803,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,0</t>
+          <t>-94,07; 44,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 197,63</t>
+          <t>-52,95; 183,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,47; 49,94</t>
+          <t>-32,09; 62,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 0,75</t>
+          <t>-20,9; 1,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 6,16</t>
+          <t>-8,8; 6,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 10,85</t>
+          <t>-12,02; 12,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 16,9</t>
+          <t>-10,82; 17,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 52,29</t>
+          <t>-94,26; 49,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 461,62</t>
+          <t>-100,0; 509,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 112,77</t>
+          <t>-53,63; 133,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,49; 78,95</t>
+          <t>-31,19; 81,37</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,55</t>
+          <t>-4,94; 3,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 2,11</t>
+          <t>-10,44; 3,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 9,12</t>
+          <t>-16,89; 10,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 16,59</t>
+          <t>-26,29; 16,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 140,39</t>
+          <t>-76,28; 167,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 62,25</t>
+          <t>-61,33; 74,97</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 10,88</t>
+          <t>-1,56; 9,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 9,68</t>
+          <t>-4,33; 8,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 7,44</t>
+          <t>-9,77; 8,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 6,34</t>
+          <t>-15,78; 7,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 483,71</t>
+          <t>-29,29; 468,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,14; 250,3</t>
+          <t>-49,28; 228,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 47,32</t>
+          <t>-40,03; 57,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 29,94</t>
+          <t>-47,37; 32,66</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 11,78</t>
+          <t>-5,9; 11,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 5,2</t>
+          <t>-6,29; 5,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 8,16</t>
+          <t>-15,07; 7,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 9,47</t>
+          <t>-18,61; 9,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 269,79</t>
+          <t>-51,49; 224,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 379,35</t>
+          <t>-76,23; 312,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,66; 48,55</t>
+          <t>-50,49; 46,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,83; 38,51</t>
+          <t>-48,28; 39,89</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 4,21</t>
+          <t>-12,86; 4,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 18,8</t>
+          <t>-2,41; 20,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 21,58</t>
+          <t>-13,29; 21,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 13,27</t>
+          <t>-24,63; 15,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 276,36</t>
+          <t>-100,0; 306,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,79; 171,76</t>
+          <t>-47,42; 186,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 35,23</t>
+          <t>-42,79; 38,43</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,23</t>
+          <t>-2,26; 4,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,27</t>
+          <t>-3,99; 2,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 4,16</t>
+          <t>-5,35; 4,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 3,51</t>
+          <t>-7,43; 3,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 83,07</t>
+          <t>-29,67; 85,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 46,45</t>
+          <t>-46,5; 50,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 26,49</t>
+          <t>-25,74; 26,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 12,42</t>
+          <t>-22,03; 13,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 11,22</t>
+          <t>-4,07; 12,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 0,16</t>
+          <t>-20,45; -0,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 15,45</t>
+          <t>-7,39; 17,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,65; 12,82</t>
+          <t>-13,47; 11,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-76,97; 803,33</t>
+          <t>-73,37; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-94,07; 44,41</t>
+          <t>-100,0; 11,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-52,95; 183,71</t>
+          <t>-43,07; 207,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 62,42</t>
+          <t>-39,46; 50,36</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,9; 1,07</t>
+          <t>-21,53; 0,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 6,54</t>
+          <t>-8,31; 6,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 12,05</t>
+          <t>-12,61; 12,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,82; 17,05</t>
+          <t>-9,56; 17,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-94,26; 49,11</t>
+          <t>-93,92; 106,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 509,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,63; 133,2</t>
+          <t>-54,62; 114,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 81,37</t>
+          <t>-30,04; 84,0</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 3,81</t>
+          <t>-4,8; 3,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 3,7</t>
+          <t>-11,21; 2,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 10,06</t>
+          <t>-15,71; 9,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 16,92</t>
+          <t>-24,46; 16,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-76,28; 167,28</t>
+          <t>-74,57; 158,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 74,97</t>
+          <t>-54,94; 65,16</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 9,98</t>
+          <t>-1,2; 10,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 8,61</t>
+          <t>-4,19; 9,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 8,32</t>
+          <t>-9,64; 7,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 7,11</t>
+          <t>-15,84; 6,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 468,47</t>
+          <t>-27,95; 473,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 228,74</t>
+          <t>-48,73; 255,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 57,31</t>
+          <t>-39,32; 48,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 32,66</t>
+          <t>-47,63; 28,77</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 11,96</t>
+          <t>-5,38; 12,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 5,21</t>
+          <t>-6,01; 5,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 7,71</t>
+          <t>-15,23; 8,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 9,61</t>
+          <t>-19,65; 11,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-51,49; 224,85</t>
+          <t>-47,9; 276,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-76,23; 312,67</t>
+          <t>-77,62; 330,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,49; 46,32</t>
+          <t>-51,07; 42,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,28; 39,89</t>
+          <t>-48,16; 43,44</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 4,37</t>
+          <t>-12,16; 5,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 20,52</t>
+          <t>-3,23; 18,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 21,44</t>
+          <t>-13,59; 20,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 15,09</t>
+          <t>-24,78; 15,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 306,9</t>
+          <t>-100,0; 313,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 186,66</t>
+          <t>-46,5; 181,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,79; 38,43</t>
+          <t>-40,98; 40,71</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,09</t>
+          <t>-2,05; 4,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,52</t>
+          <t>-3,55; 2,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 4,39</t>
+          <t>-5,07; 4,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 3,66</t>
+          <t>-8,61; 3,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 85,07</t>
+          <t>-26,18; 92,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 50,52</t>
+          <t>-44,81; 50,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 26,44</t>
+          <t>-23,71; 27,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 13,19</t>
+          <t>-24,75; 13,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-0,95%</t>
+          <t>-6,81%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 12,03</t>
+          <t>-3,48; 11,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,45; -0,97</t>
+          <t>-21,46; -0,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 17,06</t>
+          <t>-7,84; 16,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 11,56</t>
+          <t>-15,26; 10,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,37; —</t>
+          <t>-70,64; 749,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 11,44</t>
+          <t>-100,0; 32,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 207,98</t>
+          <t>-44,13; 197,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 50,36</t>
+          <t>-39,72; 38,73</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 0,44</t>
+          <t>-21,49; 0,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,2</t>
+          <t>-9,52; 6,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 12,15</t>
+          <t>-13,06; 10,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 17,7</t>
+          <t>-11,47; 16,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-93,92; 106,98</t>
+          <t>-100,0; 52,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 461,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 114,34</t>
+          <t>-58,16; 112,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 84,0</t>
+          <t>-30,43; 68,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,55</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-12,74%</t>
+          <t>-4,26%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 3,61</t>
+          <t>-4,94; 3,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 2,09</t>
+          <t>-11,0; 2,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 9,81</t>
+          <t>-18,18; 9,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 16,38</t>
+          <t>-22,95; 22,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,57; 158,89</t>
+          <t>-80,82; 140,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 65,16</t>
+          <t>-53,36; 92,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,38</t>
+          <t>-6,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-15,89%</t>
+          <t>-22,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 10,62</t>
+          <t>-0,89; 10,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 9,72</t>
+          <t>-4,33; 9,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 7,9</t>
+          <t>-10,37; 7,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 6,09</t>
+          <t>-18,43; 4,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 473,88</t>
+          <t>-22,61; 483,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 255,78</t>
+          <t>-47,14; 250,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 48,75</t>
+          <t>-40,47; 47,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 28,77</t>
+          <t>-50,81; 20,71</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,98</t>
+          <t>-4,82</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-15,18%</t>
+          <t>-13,52%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 12,96</t>
+          <t>-5,35; 11,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 5,74</t>
+          <t>-5,97; 5,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 8,14</t>
+          <t>-15,28; 8,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 11,24</t>
+          <t>-19,17; 10,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 276,62</t>
+          <t>-48,42; 269,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-77,62; 330,89</t>
+          <t>-77,72; 379,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 42,93</t>
+          <t>-48,66; 48,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,16; 43,44</t>
+          <t>-45,83; 39,25</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-5,17</t>
+          <t>-4,23</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-10,52%</t>
+          <t>-8,15%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 5,14</t>
+          <t>-13,17; 4,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 18,63</t>
+          <t>-3,12; 18,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 20,38</t>
+          <t>-13,59; 21,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 15,67</t>
+          <t>-23,29; 14,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 313,19</t>
+          <t>-100,0; 276,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 181,85</t>
+          <t>-49,79; 171,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 40,71</t>
+          <t>-37,63; 37,15</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-2,77</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-6,9%</t>
+          <t>-8,22%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,24</t>
+          <t>-2,34; 4,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 2,57</t>
+          <t>-3,98; 2,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 4,52</t>
+          <t>-5,12; 4,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 3,82</t>
+          <t>-9,22; 2,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-26,18; 92,99</t>
+          <t>-28,76; 83,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,81; 50,89</t>
+          <t>-47,73; 46,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 27,98</t>
+          <t>-23,64; 26,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 13,33</t>
+          <t>-24,99; 8,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C02-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C02-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,74</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-10,2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-69,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-6,81%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.741551873367241</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-10.19751200834737</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.890411288901377</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.176733879316695</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.9054763071167636</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.6981385804396157</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2801364525886768</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.06814599232447302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,48; 11,01</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-21,46; -0,86</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,84; 16,29</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-15,26; 10,16</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-70,64; 749,72</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 32,0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-44,13; 197,63</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-39,72; 38,73</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.481499339471306</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-21.46369587050028</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.836099848902403</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-15.25824800263755</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7063601607271832</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4413206064719846</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.3971647607618062</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.01052718990306</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-0.8644163149010201</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>16.28566038559443</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.15599847848014</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>7.497183524652539</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3199903385707056</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.976311994379436</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.3873440186512598</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-8,97</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,68</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-64,79%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-21,19%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-4,06%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-21,49; 0,75</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-9,52; 6,16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-13,06; 10,85</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,47; 16,25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 52,29</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 461,62</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-58,16; 112,77</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-30,43; 68,74</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-8.972588486528025</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.21575629079155</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6825236704163462</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.309817093132223</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.6479097493218293</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2118544425941257</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.04063648729098637</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1126010893958138</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,36</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,54</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-35,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-64,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-23,52%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-4,26%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-21.48525461123865</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-9.522624573399169</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-13.06450126756948</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.46833069097934</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.581588653136594</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3043217806813759</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,94; 3,55</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-11,0; 2,11</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-18,18; 9,12</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-22,95; 22,4</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-80,82; 140,39</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-53,36; 92,07</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7522892009794544</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.160452688587298</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10.85284238930103</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16.24910369463657</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.5228932977003425</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4.616158238665514</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.127713342333291</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.6873548815971998</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +819,191 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,09</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,69</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-6,34</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>87,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-4,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-22,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.8345813032929549</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.363224438433718</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.536622651983312</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.52344955504658</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3539336352187418</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.6463273101547748</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2352263031926549</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.04259939006134841</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 10,88</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,33; 9,68</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-10,37; 7,44</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-18,43; 4,33</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-22,61; 483,71</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-47,14; 250,3</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-40,47; 47,32</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-50,81; 20,71</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.943079470663392</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-10.99886490583924</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-18.18219877211204</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-22.94741581172947</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="n">
+        <v>-0.8081987514990515</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5335557336904592</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.553422381064307</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.112176025398341</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.123753049194621</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>22.40405347199698</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="n">
+        <v>1.403873976033789</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.9207233470355589</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,65</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,82</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,93%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-2,49%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-14,74%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-13,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,35; 11,78</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,97; 5,2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-15,28; 8,16</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-19,17; 10,72</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-48,42; 269,79</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-77,72; 379,35</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-48,66; 48,55</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-45,83; 39,25</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>4.090023711433915</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.692303684376624</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.9324245272497339</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-6.338181366077086</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.8731681798616709</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3953023544677641</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.04691465818191734</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.2199792954907354</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-3,46</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5,51</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,23</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-45,64%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>157,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-8,15%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.8935462017652617</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.325990934377824</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-10.3714893931788</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-18.42778565028568</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2261257983743681</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4714019202480998</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4047264806048704</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5081145836141435</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-13,17; 4,21</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-3,12; 18,8</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-13,59; 21,58</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-23,29; 14,99</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 276,36</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-49,79; 171,76</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-37,63; 37,15</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.8847231020199</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9.679120886408121</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.435891406651181</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.326151166848394</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4.837102145057656</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.502959800313088</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.4732269376168036</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2070940839618401</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1011,293 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,77</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-10,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-3,1%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-8,22%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>3.116283225639563</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1179320406042884</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.653284645329924</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-4.821702326806898</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.3492640271750425</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.02492954062789089</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1474354561291943</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1352041727790379</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,34; 4,23</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,98; 2,27</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 4,16</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-9,22; 2,67</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-28,76; 83,07</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-47,73; 46,45</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-23,64; 26,49</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-24,99; 8,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.353645379602901</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-5.966202490650517</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-15.27849752252441</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-19.1736794188653</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4841764288473479</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.7772143862263411</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4865753691941637</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.4583018228295082</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>11.78175887391351</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>5.196697318740235</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.159589319671191</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>10.71788176863957</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>2.697886163011964</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3.793463210596638</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.485453021414692</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.392478343881171</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-3.458186419659801</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>5.510445863519836</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>3.191138155864259</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-4.234935006416024</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4564180508291253</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1.575449054847386</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.1551724767322391</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.08153830487623989</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-13.16727191176756</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-3.123195788099478</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-13.59241006316547</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-23.286510998532</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="n">
+        <v>-0.4979285140556804</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.3762958362863237</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>4.213539577422912</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>18.80480400382459</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>21.58120563858958</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>14.98774594028386</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>2.763613623766933</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="n">
+        <v>1.717622359745328</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.3715093384138691</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.9172049806319846</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.6973069871523095</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.5938799678707446</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.770642247294858</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.143182528624243</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.1059986439811741</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.03100789470375049</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.08224988797310899</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-2.342634555204473</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.98241836125008</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-5.115401236974198</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-9.222810613453968</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.2876365082795939</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.4773165024965826</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.2364163180829643</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.2498577176207388</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4.231050996617903</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2.268485815405477</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>4.159571466937964</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.671114242543334</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.8307459159161767</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.4644565357602338</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.2648566475775476</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.08745165731609122</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1305,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
